--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487833_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487833_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MENENDEZ GARCIA</t>
+          <t>T. PIERRE PHILIPPE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7606</v>
+        <v>1.23</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8103</v>
+        <v>3.9311</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.0497</v>
+        <v>-2.7012</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.7465</v>
+        <v>5.1178</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6721</v>
+        <v>0.3581</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.0744</v>
+        <v>4.7597</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9933</v>
+        <v>8.678000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2186</v>
+        <v>2.5344</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7748</v>
+        <v>6.1436</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.7399</v>
+        <v>-3.5601</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.8907</v>
+        <v>-2.1763</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.8492</v>
+        <v>-1.3838</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2081</v>
+        <v>-4.5786</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0406</v>
+        <v>-6.4517</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2487</v>
+        <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>5.4665</v>
+        <v>1.0445</v>
       </c>
       <c r="T2" t="n">
-        <v>4.2301</v>
+        <v>0.8911</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2364</v>
+        <v>0.1534</v>
       </c>
       <c r="V2" t="n">
+        <v>-0.3538</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.8137</v>
+      </c>
+      <c r="X2" t="n">
         <v>-1.1675</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.6275</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-2.795</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. DUKE TOUSSAINT</t>
+          <t>J. MENENDEZ GARCIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9856</v>
+        <v>0.2255</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3696</v>
+        <v>5.7743</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.3839</v>
+        <v>-5.5488</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.8091</v>
+        <v>-1.7465</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.5592</v>
+        <v>-0.6721</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.2499</v>
+        <v>-1.0744</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6324</v>
+        <v>2.9933</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3189</v>
+        <v>2.2186</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3135</v>
+        <v>0.7748</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.4415</v>
+        <v>-4.7399</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.8781</v>
+        <v>-2.8907</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5634</v>
+        <v>-1.8492</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7937</v>
+        <v>2.9314</v>
       </c>
       <c r="T3" t="n">
-        <v>3.5686</v>
+        <v>2.1941</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2251</v>
+        <v>0.7373</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.8314</v>
+        <v>-1.1675</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.8314</v>
+        <v>1.6275</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2.795</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. PIERRE PHILIPPE</t>
+          <t>D. RAMÍREZ SÁNCHEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0266</v>
+        <v>-0.0915</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6453</v>
+        <v>1.1544</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.6718</v>
+        <v>-1.2458</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1178</v>
+        <v>-0.1528</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3581</v>
+        <v>-0.7014</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7597</v>
+        <v>0.5486</v>
       </c>
       <c r="J4" t="n">
-        <v>8.678000000000001</v>
+        <v>1.1701</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5344</v>
+        <v>0.552</v>
       </c>
       <c r="L4" t="n">
-        <v>6.1436</v>
+        <v>0.618</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.5601</v>
+        <v>-1.3228</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.1763</v>
+        <v>-1.2535</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3838</v>
+        <v>-0.0694</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.5786</v>
+        <v>0.4162</v>
       </c>
       <c r="Q4" t="n">
-        <v>-6.4517</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8731</v>
+        <v>0.4162</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.212</v>
+        <v>-0.3549</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3948</v>
+        <v>-0.0157</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1828</v>
+        <v>-0.3392</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. RAMÍREZ SÁNCHEZ</t>
+          <t>S. BARROS GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5494</v>
+        <v>-0.5638</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7258</v>
+        <v>3.2758</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2752</v>
+        <v>-3.8396</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1528</v>
+        <v>-2.169</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7014</v>
+        <v>-1.9274</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5486</v>
+        <v>-0.2417</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1701</v>
+        <v>2.2483</v>
       </c>
       <c r="K5" t="n">
-        <v>0.552</v>
+        <v>0.6775</v>
       </c>
       <c r="L5" t="n">
-        <v>0.618</v>
+        <v>1.5708</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3228</v>
+        <v>-4.4174</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2535</v>
+        <v>-2.6049</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0694</v>
+        <v>-1.8124</v>
       </c>
       <c r="P5" t="n">
         <v>0.4162</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.2487</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4162</v>
+        <v>1.6649</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8129</v>
+        <v>0.959</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4443</v>
+        <v>0.8787</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3686</v>
+        <v>0.0803</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5658</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="E6" t="n">
         <v>-0.1574</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4084</v>
+        <v>-0.4672</v>
       </c>
       <c r="G6" t="n">
         <v>0.0261</v>
@@ -922,13 +922,13 @@
         <v>0.4162</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0137</v>
+        <v>-0.045</v>
       </c>
       <c r="T6" t="n">
         <v>0.0124</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0013</v>
+        <v>-0.0574</v>
       </c>
       <c r="V6" t="n">
         <v>-0.8137</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. OKAFOR AUGUSTIN</t>
+          <t>J. REILLY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5492</v>
+        <v>-0.7936</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0986</v>
+        <v>1.7684</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4506</v>
+        <v>-2.5621</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7599</v>
+        <v>-3.0676</v>
       </c>
       <c r="H7" t="n">
-        <v>0.23</v>
+        <v>-2.0446</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5299</v>
+        <v>-1.023</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8988</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1934</v>
+        <v>0.0827</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7054</v>
+        <v>0.8956</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.139</v>
+        <v>-4.0459</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0366</v>
+        <v>-2.1273</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1755</v>
+        <v>-1.9186</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2893</v>
+        <v>-0.2081</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0406</v>
+        <v>1.8731</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2466</v>
+        <v>1.1928</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0619</v>
+        <v>0.9983</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3085</v>
+        <v>0.1945</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8137</v>
+        <v>-0.5838</v>
       </c>
       <c r="W7" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0437</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. REILLY</t>
+          <t>I. DUKE TOUSSAINT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7404</v>
+        <v>-0.8948</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2327</v>
+        <v>1.5479</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.9731</v>
+        <v>-2.4427</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.0676</v>
+        <v>-2.8091</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.0446</v>
+        <v>-1.5592</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.023</v>
+        <v>-1.2499</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.6324</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0827</v>
+        <v>0.3189</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8956</v>
+        <v>0.3135</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.0459</v>
+        <v>-3.4415</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.1273</v>
+        <v>-1.8781</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.9186</v>
+        <v>-1.5634</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8731</v>
+        <v>0.8325</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2459</v>
+        <v>1.9133</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4625</v>
+        <v>1.7469</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2165</v>
+        <v>0.1664</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5838</v>
+        <v>-0.8314</v>
       </c>
       <c r="W8" t="n">
+        <v>-0.8314</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.5838</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. BARROS GARCIA</t>
+          <t>M. OKAFOR AUGUSTIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4251</v>
+        <v>-1.5976</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5613</v>
+        <v>-1.2057</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.9864</v>
+        <v>-0.3919</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.169</v>
+        <v>0.7599</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9274</v>
+        <v>0.23</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2417</v>
+        <v>0.5299</v>
       </c>
       <c r="J9" t="n">
-        <v>2.2483</v>
+        <v>0.8988</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6775</v>
+        <v>0.1934</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5708</v>
+        <v>0.7054</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.4174</v>
+        <v>-0.139</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.6049</v>
+        <v>0.0366</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.8124</v>
+        <v>-0.1755</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4162</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.2487</v>
+        <v>-2.2893</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9023</v>
+        <v>-0.295</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8358</v>
+        <v>-0.0452</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0665</v>
+        <v>-0.2498</v>
       </c>
       <c r="V9" t="n">
+        <v>-0.8137</v>
+      </c>
+      <c r="W9" t="n">
         <v>0.23</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.3975</v>
-      </c>
       <c r="X9" t="n">
-        <v>-1.1675</v>
+        <v>-1.0437</v>
       </c>
     </row>
     <row r="10">
@@ -1192,10 +1192,10 @@
         <v>-3.1103</v>
       </c>
       <c r="E10" t="n">
-        <v>16.089</v>
+        <v>16.0888</v>
       </c>
       <c r="F10" t="n">
-        <v>-19.1991</v>
+        <v>-19.1993</v>
       </c>
       <c r="G10" t="n">
         <v>-4.0412</v>
@@ -1204,13 +1204,13 @@
         <v>-6.1844</v>
       </c>
       <c r="I10" t="n">
-        <v>2.143099999999999</v>
+        <v>2.1431</v>
       </c>
       <c r="J10" t="n">
         <v>17.6376</v>
       </c>
       <c r="K10" t="n">
-        <v>6.615900000000001</v>
+        <v>6.6159</v>
       </c>
       <c r="L10" t="n">
         <v>11.0217</v>
@@ -1234,13 +1234,13 @@
         <v>9.3653</v>
       </c>
       <c r="S10" t="n">
-        <v>7.345999999999998</v>
+        <v>7.3461</v>
       </c>
       <c r="T10" t="n">
-        <v>6.6606</v>
+        <v>6.660600000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6855</v>
+        <v>0.6854999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>-4.3339</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.3458</v>
+        <v>6.3737</v>
       </c>
       <c r="E11" t="n">
-        <v>8.916</v>
+        <v>9.237500000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5702</v>
+        <v>-2.8638</v>
       </c>
       <c r="G11" t="n">
         <v>5.9867</v>
@@ -1312,13 +1312,13 @@
         <v>1.4568</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2454</v>
+        <v>-1.2175</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3948</v>
+        <v>-0.0733</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8506</v>
+        <v>-1.1442</v>
       </c>
       <c r="V11" t="n">
         <v>2.2289</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ CHOCARRO</t>
+          <t>J. KNOTEK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.3306</v>
+        <v>3.0002</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5371</v>
+        <v>7.9389</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2065</v>
+        <v>-4.9387</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3479</v>
+        <v>1.6376</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2264</v>
+        <v>-0.552</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8784999999999999</v>
+        <v>2.1896</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3604</v>
+        <v>4.9487</v>
       </c>
       <c r="K12" t="n">
-        <v>1.9572</v>
+        <v>1.1956</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5968</v>
+        <v>3.7531</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0125</v>
+        <v>-3.3111</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2692</v>
+        <v>-1.7477</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2817</v>
+        <v>-1.5634</v>
       </c>
       <c r="P12" t="n">
-        <v>1.4568</v>
+        <v>1.8731</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4568</v>
+        <v>1.8731</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8279</v>
+        <v>-1.908</v>
       </c>
       <c r="T12" t="n">
-        <v>0.593</v>
+        <v>-0.3886</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.4209</v>
+        <v>-1.5194</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3538</v>
+        <v>1.3975</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5838</v>
+        <v>3.3787</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.23</v>
+        <v>-1.9813</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. KNOTEK</t>
+          <t>P. FERNANDEZ CHOCARRO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9502</v>
+        <v>2.5924</v>
       </c>
       <c r="E13" t="n">
-        <v>7.296</v>
+        <v>2.2157</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.3458</v>
+        <v>0.3767</v>
       </c>
       <c r="G13" t="n">
-        <v>1.6376</v>
+        <v>1.3479</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.552</v>
+        <v>2.2264</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1896</v>
+        <v>-0.8784999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>4.9487</v>
+        <v>1.3604</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1956</v>
+        <v>1.9572</v>
       </c>
       <c r="L13" t="n">
-        <v>3.7531</v>
+        <v>-0.5968</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.3111</v>
+        <v>-0.0125</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.7477</v>
+        <v>0.2692</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.5634</v>
+        <v>-0.2817</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8731</v>
+        <v>1.4568</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8731</v>
+        <v>1.4568</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.958</v>
+        <v>-0.5661</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0315</v>
+        <v>0.2715</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.9265</v>
+        <v>-0.8376</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3975</v>
+        <v>0.3538</v>
       </c>
       <c r="W13" t="n">
-        <v>3.3787</v>
+        <v>0.5838</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.9813</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7441</v>
+        <v>1.7021</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8193</v>
+        <v>1.605</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0752</v>
+        <v>0.097</v>
       </c>
       <c r="G14" t="n">
         <v>0.2025</v>
@@ -1546,13 +1546,13 @@
         <v>1.2487</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2929</v>
+        <v>0.2509</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.3043</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2257</v>
+        <v>-0.0535</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. DJERY</t>
+          <t>J. LACUNZA ABECIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.9478</v>
+        <v>-0.9385</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4856</v>
+        <v>1.9032</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.4333</v>
+        <v>-2.8417</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.7206</v>
+        <v>1.7037</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3221</v>
+        <v>3.7847</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.0427</v>
+        <v>-2.0811</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0108</v>
+        <v>4.8678</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7757</v>
+        <v>5.0997</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2351</v>
+        <v>-0.2319</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.7314</v>
+        <v>-3.1641</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4536</v>
+        <v>-1.3149</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.2778</v>
+        <v>-1.8492</v>
       </c>
       <c r="P15" t="n">
         <v>-0.4162</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6244</v>
+        <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4815</v>
+        <v>-1.2883</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5153</v>
+        <v>-0.4057</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0339</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7076</v>
+        <v>-0.9376</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.4776</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7076</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. LACUNZA ABECIA</t>
+          <t>J. DJERY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9575</v>
+        <v>-1.7772</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7961</v>
+        <v>0.9498</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.7536</v>
+        <v>-2.7269</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7037</v>
+        <v>-1.7206</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7847</v>
+        <v>0.3221</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.0811</v>
+        <v>-2.0427</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8678</v>
+        <v>2.0108</v>
       </c>
       <c r="K16" t="n">
-        <v>5.0997</v>
+        <v>1.7757</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.2319</v>
+        <v>0.2351</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.1641</v>
+        <v>-3.7314</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3149</v>
+        <v>-1.4536</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8492</v>
+        <v>-2.2778</v>
       </c>
       <c r="P16" t="n">
         <v>-0.4162</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6649</v>
+        <v>0.6244</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3074</v>
+        <v>-0.3479</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5129</v>
+        <v>-0.0204</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7946</v>
+        <v>-0.3275</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9376</v>
+        <v>0.7076</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.4776</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4599</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.5434</v>
+        <v>-2.7767</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0656</v>
+        <v>-1.5298</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4778</v>
+        <v>-1.2469</v>
       </c>
       <c r="G17" t="n">
         <v>-0.713</v>
@@ -1780,13 +1780,13 @@
         <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.5411</v>
+        <v>-1.7744</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9663</v>
+        <v>-0.4305</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.5748</v>
+        <v>-1.3439</v>
       </c>
       <c r="V17" t="n">
         <v>1.1675</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.8116</v>
+        <v>-4.3513</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5852</v>
+        <v>-3.121</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2264</v>
+        <v>-1.2303</v>
       </c>
       <c r="G18" t="n">
         <v>-4.4035</v>
@@ -1858,13 +1858,13 @@
         <v>1.4568</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7594</v>
+        <v>0.2197</v>
       </c>
       <c r="T18" t="n">
-        <v>0.593</v>
+        <v>0.0572</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1664</v>
+        <v>0.1625</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5838</v>
@@ -1891,22 +1891,22 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.110399999999998</v>
+        <v>3.824700000000002</v>
       </c>
       <c r="E19" t="n">
         <v>19.1993</v>
       </c>
       <c r="F19" t="n">
-        <v>-16.0888</v>
+        <v>-15.3746</v>
       </c>
       <c r="G19" t="n">
         <v>4.0413</v>
       </c>
       <c r="H19" t="n">
-        <v>6.1843</v>
+        <v>6.184299999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.1432</v>
+        <v>-2.143200000000001</v>
       </c>
       <c r="J19" t="n">
         <v>21.6789</v>
@@ -1915,7 +1915,7 @@
         <v>12.8004</v>
       </c>
       <c r="L19" t="n">
-        <v>8.878499999999999</v>
+        <v>8.878500000000001</v>
       </c>
       <c r="M19" t="n">
         <v>-17.6376</v>
@@ -1936,13 +1936,13 @@
         <v>11.4464</v>
       </c>
       <c r="S19" t="n">
-        <v>-7.346</v>
+        <v>-6.6316</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6856000000000002</v>
+        <v>-0.6854999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-6.660600000000001</v>
+        <v>-5.946200000000001</v>
       </c>
       <c r="V19" t="n">
         <v>4.3339</v>
